--- a/survey_templates/039_ux_design_user_experience_information_collection_form--survey_templates.xlsx
+++ b/survey_templates/039_ux_design_user_experience_information_collection_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'category',_'value':_'category'}</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Category', 'value': 'category'}</t>
+          <t>Category</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied', 'value': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied',_'value':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied', 'value': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied',_'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Dissatisfied', 'value': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied',_'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Very Dissatisfied', 'value': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'very_usable',_'value':_'very_usable'}</t>
+          <t>very_usable</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Very Usable', 'value': 'Very Usable'}</t>
+          <t>Very Usable</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'usable',_'value':_'usable'}</t>
+          <t>usable</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Usable', 'value': 'Usable'}</t>
+          <t>Usable</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_usable',_'value':_'somewhat_usable'}</t>
+          <t>somewhat_usable</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Usable', 'value': 'Somewhat Usable'}</t>
+          <t>Somewhat Usable</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unusable',_'value':_'somewhat_unusable'}</t>
+          <t>somewhat_unusable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unusable', 'value': 'Somewhat Unusable'}</t>
+          <t>Somewhat Unusable</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'very_unusable',_'value':_'very_unusable'}</t>
+          <t>very_unusable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unusable', 'value': 'Very Unusable'}</t>
+          <t>Very Unusable</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'early_morning',_'value':_'early_morning'}</t>
+          <t>early_morning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Early Morning', 'value': 'Early Morning'}</t>
+          <t>Early Morning</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'midday',_'value':_'midday'}</t>
+          <t>midday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Midday', 'value': 'Midday'}</t>
+          <t>Midday</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Afternoon', 'value': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Evening', 'value': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'night',_'value':_'night'}</t>
+          <t>night</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Night', 'value': 'Night'}</t>
+          <t>Night</t>
         </is>
       </c>
     </row>
